--- a/Output/Weights.xlsx
+++ b/Output/Weights.xlsx
@@ -453,17 +453,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AP28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>S&amp;P BnH</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
@@ -471,168 +475,256 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Markowitz</t>
         </is>
       </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="n"/>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
+      <c r="T1" s="1" t="n"/>
       <c r="U1" s="1" t="n"/>
       <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MAD</t>
+        </is>
+      </c>
       <c r="X1" s="1" t="n"/>
       <c r="Y1" s="1" t="n"/>
       <c r="Z1" s="1" t="n"/>
       <c r="AA1" s="1" t="n"/>
       <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="n"/>
+      <c r="AF1" s="1" t="n"/>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>MedAD</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="n"/>
+      <c r="AI1" s="1" t="n"/>
+      <c r="AJ1" s="1" t="n"/>
+      <c r="AK1" s="1" t="n"/>
+      <c r="AL1" s="1" t="n"/>
+      <c r="AM1" s="1" t="n"/>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="n"/>
+      <c r="AP1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>XLY</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>XLP</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>XLF</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>XLV</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>XLI</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>XLB</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>XLK</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>CSH</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>XLY</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>XLP</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>XLF</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>XLV</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>XLI</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>XLB</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>XLK</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>CSH</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>XLY</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>XLP</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>XLF</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>XLV</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>XLI</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>XLB</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>XLK</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>XLU</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>CSH</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>XLY</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>XLP</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="AK2" s="1" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="AL2" s="1" t="inlineStr">
+        <is>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="AM2" s="1" t="inlineStr">
+        <is>
+          <t>XLB</t>
+        </is>
+      </c>
+      <c r="AN2" s="1" t="inlineStr">
+        <is>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="AO2" s="1" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="AP2" s="1" t="inlineStr">
+        <is>
+          <t>CSH</t>
         </is>
       </c>
     </row>
@@ -648,7 +740,7 @@
         <v>2000</v>
       </c>
       <c r="B4" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>11.11</v>
@@ -675,57 +767,99 @@
         <v>11.11</v>
       </c>
       <c r="K4" t="n">
-        <v>13.69</v>
+        <v>11.11</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.73</v>
+        <v>5.12</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>9.1</v>
       </c>
       <c r="O4" t="n">
-        <v>13.1</v>
+        <v>11.97</v>
       </c>
       <c r="P4" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>7.72</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>10.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="T4" t="n">
-        <v>13.69</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>11.95</v>
       </c>
       <c r="V4" t="n">
-        <v>12.73</v>
+        <v>29.42</v>
       </c>
       <c r="W4" t="n">
-        <v>4.58</v>
+        <v>3.11</v>
       </c>
       <c r="X4" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>25</v>
+        <v>11.55</v>
       </c>
       <c r="AB4" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -734,7 +868,7 @@
         <v>2001</v>
       </c>
       <c r="B5" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
         <v>11.11</v>
@@ -761,58 +895,100 @@
         <v>11.11</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="L5" t="n">
-        <v>22.12</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>22.14</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>23.82</v>
+        <v>17.01</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>16.17</v>
       </c>
       <c r="P5" t="n">
-        <v>11.7</v>
+        <v>5.69</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S5" t="n">
-        <v>20.21</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>22.12</v>
+        <v>18.12</v>
       </c>
       <c r="V5" t="n">
-        <v>22.14</v>
+        <v>43</v>
       </c>
       <c r="W5" t="n">
-        <v>23.82</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>13.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.7</v>
+        <v>3.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.21</v>
+        <v>7.7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -820,7 +996,7 @@
         <v>2002</v>
       </c>
       <c r="B6" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>11.11</v>
@@ -847,58 +1023,100 @@
         <v>11.11</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>11.11</v>
       </c>
       <c r="L6" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>25.39</v>
       </c>
       <c r="N6" t="n">
-        <v>9.69</v>
+        <v>5.45</v>
       </c>
       <c r="O6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>8.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>3.88</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.64</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>57.06</v>
       </c>
       <c r="W6" t="n">
-        <v>9.69</v>
+        <v>18.96</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>5.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.64</v>
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="7">
@@ -906,7 +1124,7 @@
         <v>2003</v>
       </c>
       <c r="B7" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
         <v>11.11</v>
@@ -933,58 +1151,100 @@
         <v>11.11</v>
       </c>
       <c r="K7" t="n">
-        <v>10.31</v>
+        <v>11.11</v>
       </c>
       <c r="L7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>14.92</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>15.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>19.22</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="T7" t="n">
-        <v>10.31</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>14.92</v>
+        <v>74.83</v>
       </c>
       <c r="W7" t="n">
-        <v>15.54</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>22.34</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>27.13</v>
       </c>
     </row>
     <row r="8">
@@ -992,7 +1252,7 @@
         <v>2004</v>
       </c>
       <c r="B8" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
         <v>11.11</v>
@@ -1019,58 +1279,100 @@
         <v>11.11</v>
       </c>
       <c r="K8" t="n">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="L8" t="n">
-        <v>11.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>11.1</v>
+        <v>4.38</v>
       </c>
       <c r="N8" t="n">
-        <v>11.12</v>
+        <v>13.26</v>
       </c>
       <c r="O8" t="n">
-        <v>11.07</v>
+        <v>14.77</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>4.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.14</v>
+        <v>9.98</v>
       </c>
       <c r="R8" t="n">
-        <v>11.15</v>
+        <v>7.38</v>
       </c>
       <c r="S8" t="n">
-        <v>11.11</v>
+        <v>6.74</v>
       </c>
       <c r="T8" t="n">
-        <v>11.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>11.05</v>
+        <v>11.78</v>
       </c>
       <c r="V8" t="n">
-        <v>11.1</v>
+        <v>26.16</v>
       </c>
       <c r="W8" t="n">
-        <v>11.12</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>11.07</v>
+        <v>13.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.14</v>
+        <v>4.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.15</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.11</v>
+        <v>7.46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1078,7 +1380,7 @@
         <v>2005</v>
       </c>
       <c r="B9" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
         <v>11.11</v>
@@ -1108,55 +1410,97 @@
         <v>11.11</v>
       </c>
       <c r="L9" t="n">
-        <v>11.09</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>11.18</v>
+        <v>10.1</v>
       </c>
       <c r="N9" t="n">
-        <v>11.1</v>
+        <v>8.6</v>
       </c>
       <c r="O9" t="n">
-        <v>11.06</v>
+        <v>15.8</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>9.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.11</v>
+        <v>6.69</v>
       </c>
       <c r="R9" t="n">
-        <v>11.08</v>
+        <v>11.43</v>
       </c>
       <c r="S9" t="n">
-        <v>11.14</v>
+        <v>10.35</v>
       </c>
       <c r="T9" t="n">
-        <v>11.11</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>11.09</v>
+        <v>13.07</v>
       </c>
       <c r="V9" t="n">
-        <v>11.18</v>
+        <v>6.31</v>
       </c>
       <c r="W9" t="n">
-        <v>11.1</v>
+        <v>9.48</v>
       </c>
       <c r="X9" t="n">
-        <v>11.06</v>
+        <v>12.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.12</v>
+        <v>4.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.11</v>
+        <v>10.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.08</v>
+        <v>9.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.14</v>
+        <v>9.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1164,7 +1508,7 @@
         <v>2006</v>
       </c>
       <c r="B10" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
         <v>11.11</v>
@@ -1191,58 +1535,100 @@
         <v>11.11</v>
       </c>
       <c r="K10" t="n">
-        <v>4.34</v>
+        <v>11.11</v>
       </c>
       <c r="L10" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.44</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>10.46</v>
+        <v>21.33</v>
       </c>
       <c r="P10" t="n">
-        <v>8.84</v>
+        <v>9.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.74</v>
+        <v>12.13</v>
       </c>
       <c r="R10" t="n">
-        <v>7.41</v>
+        <v>6.82</v>
       </c>
       <c r="S10" t="n">
-        <v>15.01</v>
+        <v>4.87</v>
       </c>
       <c r="T10" t="n">
-        <v>4.34</v>
+        <v>5.79</v>
       </c>
       <c r="U10" t="n">
-        <v>8.75</v>
+        <v>14.46</v>
       </c>
       <c r="V10" t="n">
-        <v>25</v>
+        <v>14.81</v>
       </c>
       <c r="W10" t="n">
-        <v>10.44</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>10.46</v>
+        <v>11.98</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.84</v>
+        <v>1.76</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.74</v>
+        <v>10.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.41</v>
+        <v>11.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.01</v>
+        <v>10.36</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1250,7 +1636,7 @@
         <v>2007</v>
       </c>
       <c r="B11" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C11" t="n">
         <v>11.11</v>
@@ -1277,58 +1663,100 @@
         <v>11.11</v>
       </c>
       <c r="K11" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="L11" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>11.13</v>
+        <v>10.01</v>
       </c>
       <c r="N11" t="n">
-        <v>11.12</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>11.08</v>
+        <v>10.02</v>
       </c>
       <c r="P11" t="n">
-        <v>11.1</v>
+        <v>10.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.12</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>11.13</v>
+        <v>10.02</v>
       </c>
       <c r="T11" t="n">
-        <v>11.12</v>
+        <v>9.99</v>
       </c>
       <c r="U11" t="n">
-        <v>11.1</v>
+        <v>10.02</v>
       </c>
       <c r="V11" t="n">
-        <v>11.13</v>
+        <v>9.94</v>
       </c>
       <c r="W11" t="n">
-        <v>11.12</v>
+        <v>10.25</v>
       </c>
       <c r="X11" t="n">
-        <v>11.08</v>
+        <v>11.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.1</v>
+        <v>3.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.12</v>
+        <v>10.49</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.1</v>
+        <v>11.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.13</v>
+        <v>10.34</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.94</v>
       </c>
     </row>
     <row r="12">
@@ -1336,7 +1764,7 @@
         <v>2008</v>
       </c>
       <c r="B12" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C12" t="n">
         <v>11.11</v>
@@ -1363,58 +1791,100 @@
         <v>11.11</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>10.82</v>
       </c>
-      <c r="M12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P12" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="R12" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="S12" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" t="n">
-        <v>10.82</v>
+        <v>12.16</v>
       </c>
       <c r="V12" t="n">
-        <v>25</v>
+        <v>25.59</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>7.66</v>
+        <v>17.54</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.73</v>
+        <v>4.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>17.27</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.88</v>
+        <v>14.34</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.64</v>
+        <v>10.34</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1422,7 +1892,7 @@
         <v>2009</v>
       </c>
       <c r="B13" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C13" t="n">
         <v>11.11</v>
@@ -1449,22 +1919,22 @@
         <v>11.11</v>
       </c>
       <c r="K13" t="n">
-        <v>15.03</v>
+        <v>11.11</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>14.85</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>17.56</v>
       </c>
       <c r="O13" t="n">
-        <v>23.42</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1473,34 +1943,76 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>14.41</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.67</v>
+        <v>82.44</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>20.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>24.97</v>
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>71.63</v>
       </c>
     </row>
     <row r="14">
@@ -1508,7 +2020,7 @@
         <v>2010</v>
       </c>
       <c r="B14" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
         <v>11.11</v>
@@ -1535,57 +2047,99 @@
         <v>11.11</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>11.11</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.36</v>
+        <v>6.04</v>
       </c>
       <c r="N14" t="n">
-        <v>21.33</v>
+        <v>8.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>7.84</v>
       </c>
       <c r="R14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>8.91</v>
       </c>
       <c r="T14" t="n">
-        <v>20.41</v>
+        <v>12.83</v>
       </c>
       <c r="U14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.19</v>
+        <v>55.72</v>
       </c>
       <c r="W14" t="n">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>6.28</v>
+        <v>18.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>15.06</v>
       </c>
       <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1594,7 +2148,7 @@
         <v>2011</v>
       </c>
       <c r="B15" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C15" t="n">
         <v>11.11</v>
@@ -1621,58 +2175,100 @@
         <v>11.11</v>
       </c>
       <c r="K15" t="n">
-        <v>11.15</v>
+        <v>11.11</v>
       </c>
       <c r="L15" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>11.13</v>
+        <v>5.92</v>
       </c>
       <c r="N15" t="n">
-        <v>11.1</v>
+        <v>17.43</v>
       </c>
       <c r="O15" t="n">
-        <v>11.06</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>11.15</v>
+        <v>0.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.13</v>
+        <v>14.12</v>
       </c>
       <c r="R15" t="n">
-        <v>11.1</v>
+        <v>3.53</v>
       </c>
       <c r="S15" t="n">
-        <v>11.07</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
-        <v>11.15</v>
+        <v>8.52</v>
       </c>
       <c r="U15" t="n">
-        <v>11.1</v>
+        <v>14.37</v>
       </c>
       <c r="V15" t="n">
-        <v>11.13</v>
+        <v>31.72</v>
       </c>
       <c r="W15" t="n">
-        <v>11.1</v>
+        <v>6.6</v>
       </c>
       <c r="X15" t="n">
-        <v>11.06</v>
+        <v>17.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.15</v>
+        <v>3.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.13</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.1</v>
+        <v>13.18</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.07</v>
+        <v>5.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1680,7 +2276,7 @@
         <v>2012</v>
       </c>
       <c r="B16" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C16" t="n">
         <v>11.11</v>
@@ -1707,58 +2303,100 @@
         <v>11.11</v>
       </c>
       <c r="K16" t="n">
-        <v>13.03</v>
+        <v>11.11</v>
       </c>
       <c r="L16" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>12.27</v>
+        <v>4.46</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>19.16</v>
       </c>
       <c r="O16" t="n">
-        <v>17.15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>11.21</v>
       </c>
       <c r="R16" t="n">
-        <v>10.01</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>21.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>13.03</v>
+        <v>7.07</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>17.92</v>
       </c>
       <c r="V16" t="n">
-        <v>12.27</v>
+        <v>40.18</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="X16" t="n">
-        <v>17.15</v>
+        <v>18.34</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.01</v>
+        <v>12.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>21.95</v>
+        <v>0.66</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1766,7 +2404,7 @@
         <v>2013</v>
       </c>
       <c r="B17" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C17" t="n">
         <v>11.11</v>
@@ -1793,58 +2431,100 @@
         <v>11.11</v>
       </c>
       <c r="K17" t="n">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="L17" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>11.08</v>
+        <v>9.49</v>
       </c>
       <c r="N17" t="n">
-        <v>11.16</v>
+        <v>11.33</v>
       </c>
       <c r="O17" t="n">
-        <v>11.12</v>
+        <v>7.96</v>
       </c>
       <c r="P17" t="n">
-        <v>11.11</v>
+        <v>8.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.11</v>
+        <v>10.64</v>
       </c>
       <c r="R17" t="n">
-        <v>11.11</v>
+        <v>8.76</v>
       </c>
       <c r="S17" t="n">
-        <v>11.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>11.14</v>
+        <v>9.23</v>
       </c>
       <c r="U17" t="n">
-        <v>11.1</v>
+        <v>12.07</v>
       </c>
       <c r="V17" t="n">
-        <v>11.08</v>
+        <v>14.07</v>
       </c>
       <c r="W17" t="n">
-        <v>11.16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>11.12</v>
+        <v>12.86</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.11</v>
+        <v>5.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.11</v>
+        <v>6.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.11</v>
+        <v>11.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.06</v>
+        <v>7.99</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1852,7 +2532,7 @@
         <v>2014</v>
       </c>
       <c r="B18" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
         <v>11.11</v>
@@ -1879,58 +2559,100 @@
         <v>11.11</v>
       </c>
       <c r="K18" t="n">
-        <v>11.15</v>
+        <v>11.11</v>
       </c>
       <c r="L18" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>11.1</v>
+        <v>19.66</v>
       </c>
       <c r="N18" t="n">
-        <v>11.13</v>
+        <v>11.27</v>
       </c>
       <c r="O18" t="n">
-        <v>11.14</v>
+        <v>1.98</v>
       </c>
       <c r="P18" t="n">
-        <v>11.14</v>
+        <v>7.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.1</v>
+        <v>22.37</v>
       </c>
       <c r="R18" t="n">
-        <v>11.1</v>
+        <v>16.43</v>
       </c>
       <c r="S18" t="n">
-        <v>11.05</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>11.15</v>
+        <v>10.78</v>
       </c>
       <c r="U18" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>11.1</v>
+        <v>9.67</v>
       </c>
       <c r="W18" t="n">
-        <v>11.13</v>
+        <v>9.15</v>
       </c>
       <c r="X18" t="n">
-        <v>11.14</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.14</v>
+        <v>7.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.1</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.05</v>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1938,7 +2660,7 @@
         <v>2015</v>
       </c>
       <c r="B19" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C19" t="n">
         <v>11.11</v>
@@ -1965,58 +2687,100 @@
         <v>11.11</v>
       </c>
       <c r="K19" t="n">
-        <v>9.369999999999999</v>
+        <v>11.11</v>
       </c>
       <c r="L19" t="n">
-        <v>12.17</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>12.05</v>
+        <v>15.71</v>
       </c>
       <c r="O19" t="n">
-        <v>16.73</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>9.85</v>
+        <v>8.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.289999999999999</v>
+        <v>23.17</v>
       </c>
       <c r="R19" t="n">
-        <v>13.34</v>
+        <v>0.22</v>
       </c>
       <c r="S19" t="n">
-        <v>18.21</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>9.369999999999999</v>
+        <v>13.94</v>
       </c>
       <c r="U19" t="n">
-        <v>12.17</v>
+        <v>36.29</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W19" t="n">
-        <v>12.05</v>
+        <v>8.31</v>
       </c>
       <c r="X19" t="n">
-        <v>16.73</v>
+        <v>13.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.289999999999999</v>
+        <v>10.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.34</v>
+        <v>11.19</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.21</v>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2024,7 +2788,7 @@
         <v>2016</v>
       </c>
       <c r="B20" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
         <v>11.11</v>
@@ -2051,58 +2815,100 @@
         <v>11.11</v>
       </c>
       <c r="K20" t="n">
-        <v>16.97</v>
+        <v>11.11</v>
       </c>
       <c r="L20" t="n">
-        <v>15.27</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>19.53</v>
       </c>
       <c r="N20" t="n">
-        <v>11.09</v>
+        <v>19.42</v>
       </c>
       <c r="O20" t="n">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.28</v>
+        <v>14.31</v>
       </c>
       <c r="R20" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>16.97</v>
+        <v>11.13</v>
       </c>
       <c r="U20" t="n">
-        <v>15.27</v>
+        <v>3.88</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>31.73</v>
       </c>
       <c r="W20" t="n">
-        <v>11.09</v>
+        <v>8.84</v>
       </c>
       <c r="X20" t="n">
-        <v>15.63</v>
+        <v>13.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.28</v>
+        <v>6.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>14.9</v>
+        <v>5.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.300000000000001</v>
+        <v>9.32</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10.09</v>
       </c>
     </row>
     <row r="21">
@@ -2110,7 +2916,7 @@
         <v>2017</v>
       </c>
       <c r="B21" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
         <v>11.11</v>
@@ -2137,58 +2943,100 @@
         <v>11.11</v>
       </c>
       <c r="K21" t="n">
-        <v>2.26</v>
+        <v>11.11</v>
       </c>
       <c r="L21" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>18.78</v>
+        <v>11.88</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="P21" t="n">
-        <v>15.88</v>
+        <v>7.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.47</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>11.34</v>
+        <v>8.99</v>
       </c>
       <c r="S21" t="n">
-        <v>12.43</v>
+        <v>7.71</v>
       </c>
       <c r="T21" t="n">
-        <v>2.26</v>
+        <v>9.02</v>
       </c>
       <c r="U21" t="n">
-        <v>0.85</v>
+        <v>13.15</v>
       </c>
       <c r="V21" t="n">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="W21" t="n">
-        <v>18.78</v>
+        <v>10.4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>12.86</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.88</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.47</v>
+        <v>6.37</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.34</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.43</v>
+        <v>10.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2196,7 +3044,7 @@
         <v>2018</v>
       </c>
       <c r="B22" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C22" t="n">
         <v>11.11</v>
@@ -2223,58 +3071,100 @@
         <v>11.11</v>
       </c>
       <c r="K22" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="L22" t="n">
-        <v>11.09</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>11.04</v>
+        <v>13.05</v>
       </c>
       <c r="N22" t="n">
-        <v>11.12</v>
+        <v>7.81</v>
       </c>
       <c r="O22" t="n">
-        <v>11.12</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>11.13</v>
+        <v>12.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.13</v>
+        <v>12.55</v>
       </c>
       <c r="R22" t="n">
-        <v>11.16</v>
+        <v>13.69</v>
       </c>
       <c r="S22" t="n">
-        <v>11.09</v>
+        <v>13.78</v>
       </c>
       <c r="T22" t="n">
-        <v>11.12</v>
+        <v>18.74</v>
       </c>
       <c r="U22" t="n">
-        <v>11.09</v>
+        <v>7.41</v>
       </c>
       <c r="V22" t="n">
-        <v>11.04</v>
+        <v>0.01</v>
       </c>
       <c r="W22" t="n">
-        <v>11.12</v>
+        <v>13.05</v>
       </c>
       <c r="X22" t="n">
-        <v>11.12</v>
+        <v>7.81</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>11.13</v>
+        <v>12.96</v>
       </c>
       <c r="AA22" t="n">
-        <v>11.16</v>
+        <v>12.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.09</v>
+        <v>13.69</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="23">
@@ -2282,7 +3172,7 @@
         <v>2019</v>
       </c>
       <c r="B23" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
         <v>11.11</v>
@@ -2309,58 +3199,100 @@
         <v>11.11</v>
       </c>
       <c r="K23" t="n">
-        <v>22.85</v>
+        <v>11.11</v>
       </c>
       <c r="L23" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0.48</v>
+        <v>9.32</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>13.78</v>
       </c>
       <c r="R23" t="n">
-        <v>19.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>22.85</v>
+        <v>16.27</v>
       </c>
       <c r="U23" t="n">
-        <v>7.28</v>
+        <v>24.02</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>27.42</v>
       </c>
       <c r="W23" t="n">
-        <v>0.48</v>
+        <v>11.36</v>
       </c>
       <c r="X23" t="n">
-        <v>25</v>
+        <v>10.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>19.37</v>
+        <v>16.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>25</v>
+        <v>0.08</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14.69</v>
       </c>
     </row>
     <row r="24">
@@ -2368,7 +3300,7 @@
         <v>2020</v>
       </c>
       <c r="B24" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
         <v>11.11</v>
@@ -2398,55 +3330,97 @@
         <v>11.11</v>
       </c>
       <c r="L24" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>11.06</v>
+        <v>9.69</v>
       </c>
       <c r="N24" t="n">
-        <v>11.13</v>
+        <v>10.56</v>
       </c>
       <c r="O24" t="n">
-        <v>11.09</v>
+        <v>9.26</v>
       </c>
       <c r="P24" t="n">
-        <v>11.12</v>
+        <v>9.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>11.1</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>11.18</v>
+        <v>9.43</v>
       </c>
       <c r="S24" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="T24" t="n">
-        <v>11.11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>11.11</v>
+        <v>11.22</v>
       </c>
       <c r="V24" t="n">
-        <v>11.06</v>
+        <v>11.5</v>
       </c>
       <c r="W24" t="n">
-        <v>11.13</v>
+        <v>9.67</v>
       </c>
       <c r="X24" t="n">
-        <v>11.09</v>
+        <v>13.59</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.12</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>11.18</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.1</v>
+        <v>8.23</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2454,7 +3428,7 @@
         <v>2021</v>
       </c>
       <c r="B25" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C25" t="n">
         <v>11.11</v>
@@ -2481,57 +3455,99 @@
         <v>11.11</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
+        <v>11.11</v>
       </c>
       <c r="L25" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="N25" t="n">
-        <v>1.58</v>
+        <v>16.38</v>
       </c>
       <c r="O25" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>11.37</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.27</v>
+        <v>11.18</v>
       </c>
       <c r="R25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.92</v>
+        <v>0.37</v>
       </c>
       <c r="T25" t="n">
-        <v>25</v>
+        <v>1.24</v>
       </c>
       <c r="U25" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>64.84</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>13.48</v>
       </c>
       <c r="X25" t="n">
-        <v>11.69</v>
+        <v>7.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>10.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.04</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2540,7 +3556,7 @@
         <v>2022</v>
       </c>
       <c r="B26" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
         <v>11.11</v>
@@ -2567,57 +3583,99 @@
         <v>11.11</v>
       </c>
       <c r="K26" t="n">
-        <v>11.87</v>
+        <v>11.11</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>22.67</v>
+        <v>11.81</v>
       </c>
       <c r="O26" t="n">
-        <v>6.98</v>
+        <v>6.28</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>10.72</v>
+        <v>11.79</v>
       </c>
       <c r="R26" t="n">
-        <v>22.76</v>
+        <v>8.56</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>11.87</v>
+        <v>9.34</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="V26" t="n">
-        <v>25</v>
+        <v>14.98</v>
       </c>
       <c r="W26" t="n">
-        <v>22.67</v>
+        <v>6.29</v>
       </c>
       <c r="X26" t="n">
-        <v>6.98</v>
+        <v>15.27</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>10.72</v>
+        <v>4.92</v>
       </c>
       <c r="AA26" t="n">
-        <v>22.76</v>
+        <v>14.24</v>
       </c>
       <c r="AB26" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2626,7 +3684,7 @@
         <v>2023</v>
       </c>
       <c r="B27" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
         <v>11.11</v>
@@ -2653,58 +3711,100 @@
         <v>11.11</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="L27" t="n">
-        <v>14.38</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>9.75</v>
+        <v>6.61</v>
       </c>
       <c r="O27" t="n">
-        <v>13.84</v>
+        <v>27.37</v>
       </c>
       <c r="P27" t="n">
-        <v>12.27</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>15.91</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>14.38</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>25</v>
+        <v>66.02</v>
       </c>
       <c r="W27" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>13.84</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.27</v>
+        <v>28.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>15.91</v>
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2712,7 +3812,7 @@
         <v>2024</v>
       </c>
       <c r="B28" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="C28" t="n">
         <v>11.11</v>
@@ -2739,65 +3839,108 @@
         <v>11.11</v>
       </c>
       <c r="K28" t="n">
-        <v>24.99</v>
+        <v>11.11</v>
       </c>
       <c r="L28" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.66</v>
+        <v>8.08</v>
       </c>
       <c r="N28" t="n">
-        <v>11.17</v>
+        <v>11.62</v>
       </c>
       <c r="O28" t="n">
-        <v>5.11</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>14.26</v>
+        <v>8.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>11.46</v>
+        <v>11.34</v>
       </c>
       <c r="R28" t="n">
-        <v>25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>24.99</v>
+        <v>9.48</v>
       </c>
       <c r="U28" t="n">
-        <v>3.36</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="V28" t="n">
-        <v>4.66</v>
+        <v>15.65</v>
       </c>
       <c r="W28" t="n">
-        <v>11.17</v>
+        <v>14.12</v>
       </c>
       <c r="X28" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.26</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>11.46</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="T1:AB1"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="K1:S1"/>
+  <mergeCells count="4">
+    <mergeCell ref="W1:AF1"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="AG1:AP1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
